--- a/data/excel/assessment_centers.xlsx
+++ b/data/excel/assessment_centers.xlsx
@@ -202,7 +202,7 @@
     <col min="3" max="3" width="52" customWidth="1"/>
     <col min="4" max="4" width="52" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="11.700000000000001" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="35.1" customWidth="1"/>
     <col min="8" max="8" width="35.1" customWidth="1"/>
     <col min="9" max="9" width="52" customWidth="1"/>
@@ -5823,6 +5823,258 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c t="inlineStr" r="A90">
+        <is>
+          <t>Region VIII - Eastern Visayas</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B90">
+        <is>
+          <t>Southern Leyte</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C90">
+        <is>
+          <t>SAINT JOSEPH COLLEGE,MAASIN,LEYTE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D90">
+        <is>
+          <t>Brgy. Mambajao, Maasin City, Southern Leyte</t>
+        </is>
+      </c>
+      <c t="n" r="E90">
+        <v>124.840341</v>
+      </c>
+      <c t="n" r="F90">
+        <v>10.165355</v>
+      </c>
+      <c t="inlineStr" r="G90">
+        <is>
+          <t>Epifanio O. Amora, Jr.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H90">
+        <is>
+          <t>09178364531</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I90">
+        <is>
+          <t>Human Health / Health Care</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J90">
+        <is>
+          <t>Barangay Health Services NC II</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K90">
+        <is>
+          <t>AC-BHS0208642527147</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="L90">
+        <is>
+          <t>8/15/2025</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M90">
+        <is>
+          <t>8/15/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c t="inlineStr" r="A91">
+        <is>
+          <t>Region VIII - Eastern Visayas</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B91">
+        <is>
+          <t>Southern Leyte</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C91">
+        <is>
+          <t>STI  COLLEGE MAASIN, INC.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D91">
+        <is>
+          <t>Brgy. Tunga-tunga, Maasin City, Southern Leyte</t>
+        </is>
+      </c>
+      <c t="n" r="E91">
+        <v>10.135616</v>
+      </c>
+      <c t="n" r="F91">
+        <v>124.825452</v>
+      </c>
+      <c t="inlineStr" r="G91">
+        <is>
+          <t>Donn Justin O. Bulos</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H91">
+        <is>
+          <t>09173061410</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I91">
+        <is>
+          <t>Tourism (Hotel and Restaurant)</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J91">
+        <is>
+          <t>Cookery NC II</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K91">
+        <is>
+          <t>AC-COK0208642628131</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="L91">
+        <is>
+          <t>10/7/2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M91">
+        <is>
+          <t>10/7/2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c t="inlineStr" r="A92">
+        <is>
+          <t>Region VIII - Eastern Visayas</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B92">
+        <is>
+          <t>Southern Leyte</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C92">
+        <is>
+          <t>ARC TUTORIALS LEARNING SERVICES INC.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D92">
+        <is>
+          <t>08 Caday Street  Zone I (pob.) Sogod, Southern Leyte</t>
+        </is>
+      </c>
+      <c t="n" r="E92">
+        <v>10.3858</v>
+      </c>
+      <c t="n" r="F92">
+        <v>124.9796</v>
+      </c>
+      <c t="inlineStr" r="G92">
+        <is>
+          <t>Venancio T. Estinozo</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H92">
+        <is>
+          <t>(053) 577-8034 /09280751537</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I92">
+        <is>
+          <t>Visual Arts</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J92">
+        <is>
+          <t>Photography NC II</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K92">
+        <is>
+          <t>AC-PHO0208642628132</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="L92">
+        <is>
+          <t>10/7/2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M92">
+        <is>
+          <t>10/7/2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c t="inlineStr" r="A93">
+        <is>
+          <t>Region VIII - Eastern Visayas</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B93">
+        <is>
+          <t>Southern Leyte</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C93">
+        <is>
+          <t>ARC TUTORIALS LEARNING SERVICES INC.</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="D93">
+        <is>
+          <t>08 Caday Street  Zone I (pob.) Sogod, Southern Leyte</t>
+        </is>
+      </c>
+      <c t="n" r="E93">
+        <v>10.3858</v>
+      </c>
+      <c t="n" r="F93">
+        <v>124.9796</v>
+      </c>
+      <c t="inlineStr" r="G93">
+        <is>
+          <t>Venancio T. Estinozo</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="H93">
+        <is>
+          <t>(053) 577-8034 /09280751537</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I93">
+        <is>
+          <t>Information and Communication Technology</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J93">
+        <is>
+          <t>Visual Graphic Design NC III</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="K93">
+        <is>
+          <t>AC-VGD0308642628133</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="L93">
+        <is>
+          <t>10/7/2026</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M93">
+        <is>
+          <t>10/7/2028</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>